--- a/data/stats_jardins_productifs/stats_Dominique_2025.xlsx
+++ b/data/stats_jardins_productifs/stats_Dominique_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antoi\Documents\VSC Carte Jardin Strasbourg\data\stats_jardins_productifs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D69BC4-FA5B-451E-8931-3CCC3D5BE735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0873E83A-5DB2-44F7-9AF7-D418775BA428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -1496,16 +1496,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>809625</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>96837</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>615950</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>115887</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>131762</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>615950</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>150812</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
